--- a/data/13 Week production 2026-09-28 based on Template.xlsx
+++ b/data/13 Week production 2026-09-28 based on Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aprasad\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4A43304-8230-492C-8C90-F02A027D6F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{D4A43304-8230-492C-8C90-F02A027D6F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B72A1319-2D28-4676-B934-B2CB7D84D0E9}"/>
   <bookViews>
-    <workbookView xWindow="12090" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11244" yWindow="-17472" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Club Pack Biweekly Fluid" sheetId="1" r:id="rId1"/>
@@ -3133,7 +3133,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3182,6 +3182,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -3210,7 +3216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3244,6 +3250,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3579,15 +3589,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB469"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
     <col min="15" max="28" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
@@ -3673,7 +3683,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>
@@ -3759,7 +3769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
@@ -3845,7 +3855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>47</v>
       </c>
@@ -3931,7 +3941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>49</v>
       </c>
@@ -4017,7 +4027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>51</v>
       </c>
@@ -4103,7 +4113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>53</v>
       </c>
@@ -4189,7 +4199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -4275,7 +4285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>57</v>
       </c>
@@ -4361,7 +4371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>59</v>
       </c>
@@ -4447,7 +4457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>61</v>
       </c>
@@ -4533,7 +4543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>63</v>
       </c>
@@ -4619,7 +4629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
@@ -4705,7 +4715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>67</v>
       </c>
@@ -4791,7 +4801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>69</v>
       </c>
@@ -4877,7 +4887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>71</v>
       </c>
@@ -4963,7 +4973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>73</v>
       </c>
@@ -5049,7 +5059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>75</v>
       </c>
@@ -5135,7 +5145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>77</v>
       </c>
@@ -5221,7 +5231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>79</v>
       </c>
@@ -5307,7 +5317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>81</v>
       </c>
@@ -5393,7 +5403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>83</v>
       </c>
@@ -5479,7 +5489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>85</v>
       </c>
@@ -5565,7 +5575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>87</v>
       </c>
@@ -5651,7 +5661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>89</v>
       </c>
@@ -5737,7 +5747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>91</v>
       </c>
@@ -5823,7 +5833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>93</v>
       </c>
@@ -5909,7 +5919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>95</v>
       </c>
@@ -5995,7 +6005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>97</v>
       </c>
@@ -6081,7 +6091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>99</v>
       </c>
@@ -6167,7 +6177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>101</v>
       </c>
@@ -6253,7 +6263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>103</v>
       </c>
@@ -6339,7 +6349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>105</v>
       </c>
@@ -6425,7 +6435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>107</v>
       </c>
@@ -6511,7 +6521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>109</v>
       </c>
@@ -6597,7 +6607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>111</v>
       </c>
@@ -6683,7 +6693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>113</v>
       </c>
@@ -6769,7 +6779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
@@ -6855,7 +6865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>117</v>
       </c>
@@ -6941,7 +6951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>119</v>
       </c>
@@ -7027,7 +7037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>121</v>
       </c>
@@ -7113,93 +7123,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:28" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="19">
         <v>11360</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="19">
         <v>11214</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="19">
         <v>10152</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="19">
         <v>6888</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="19">
         <v>15596</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="19">
         <v>13482</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="19">
         <v>15176</v>
       </c>
-      <c r="J42" s="9">
+      <c r="J42" s="19">
         <v>16540</v>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="19">
         <v>14589</v>
       </c>
-      <c r="L42" s="9">
+      <c r="L42" s="19">
         <v>12474</v>
       </c>
-      <c r="M42" s="9">
+      <c r="M42" s="19">
         <v>14112</v>
       </c>
-      <c r="N42" s="9">
+      <c r="N42" s="19">
         <v>15176</v>
       </c>
-      <c r="O42" s="9">
+      <c r="O42" s="19">
         <v>156759</v>
       </c>
-      <c r="P42" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="11">
-        <v>0</v>
-      </c>
-      <c r="R42" s="11">
+      <c r="P42" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="19">
+        <v>0</v>
+      </c>
+      <c r="R42" s="19">
         <v>1265</v>
       </c>
-      <c r="S42" s="11">
+      <c r="S42" s="19">
         <v>3763</v>
       </c>
-      <c r="T42" s="11">
+      <c r="T42" s="19">
         <v>3763</v>
       </c>
-      <c r="U42" s="11">
+      <c r="U42" s="19">
         <v>3763</v>
       </c>
-      <c r="V42" s="11">
+      <c r="V42" s="19">
         <v>2823</v>
       </c>
-      <c r="W42" s="11">
+      <c r="W42" s="19">
         <v>4047</v>
       </c>
-      <c r="X42" s="11">
+      <c r="X42" s="19">
         <v>4047</v>
       </c>
-      <c r="Y42" s="11">
+      <c r="Y42" s="19">
         <v>4047</v>
       </c>
-      <c r="Z42" s="11">
+      <c r="Z42" s="19">
         <v>3035</v>
       </c>
-      <c r="AA42" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AA42" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>125</v>
       </c>
@@ -7285,7 +7295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>127</v>
       </c>
@@ -7371,7 +7381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>129</v>
       </c>
@@ -7457,7 +7467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>130</v>
       </c>
@@ -7543,7 +7553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>132</v>
       </c>
@@ -7629,7 +7639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>134</v>
       </c>
@@ -7715,7 +7725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>136</v>
       </c>
@@ -7801,7 +7811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>138</v>
       </c>
@@ -7887,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>140</v>
       </c>
@@ -7973,7 +7983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>142</v>
       </c>
@@ -8059,7 +8069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>144</v>
       </c>
@@ -8145,7 +8155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>146</v>
       </c>
@@ -8231,7 +8241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>148</v>
       </c>
@@ -8317,7 +8327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>150</v>
       </c>
@@ -8403,7 +8413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>152</v>
       </c>
@@ -8489,7 +8499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>154</v>
       </c>
@@ -8575,7 +8585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>156</v>
       </c>
@@ -8661,7 +8671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>158</v>
       </c>
@@ -8747,7 +8757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>160</v>
       </c>
@@ -8833,7 +8843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>162</v>
       </c>
@@ -8919,7 +8929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>164</v>
       </c>
@@ -9005,7 +9015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>166</v>
       </c>
@@ -9091,7 +9101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>168</v>
       </c>
@@ -9177,7 +9187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>170</v>
       </c>
@@ -9263,7 +9273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>172</v>
       </c>
@@ -9349,7 +9359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>174</v>
       </c>
@@ -9435,7 +9445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>176</v>
       </c>
@@ -9521,7 +9531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>178</v>
       </c>
@@ -9607,7 +9617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>180</v>
       </c>
@@ -9693,7 +9703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>182</v>
       </c>
@@ -9779,7 +9789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>184</v>
       </c>
@@ -9865,7 +9875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>186</v>
       </c>
@@ -9951,7 +9961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>188</v>
       </c>
@@ -10037,7 +10047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>190</v>
       </c>
@@ -10123,7 +10133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>192</v>
       </c>
@@ -10209,7 +10219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>194</v>
       </c>
@@ -10295,7 +10305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>196</v>
       </c>
@@ -10381,7 +10391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>198</v>
       </c>
@@ -10467,7 +10477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>200</v>
       </c>
@@ -10553,7 +10563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>202</v>
       </c>
@@ -10639,7 +10649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>204</v>
       </c>
@@ -10725,7 +10735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>206</v>
       </c>
@@ -10811,7 +10821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>208</v>
       </c>
@@ -10897,7 +10907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>210</v>
       </c>
@@ -10983,7 +10993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>212</v>
       </c>
@@ -11069,7 +11079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>214</v>
       </c>
@@ -11155,7 +11165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>216</v>
       </c>
@@ -11241,7 +11251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>218</v>
       </c>
@@ -11327,7 +11337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>220</v>
       </c>
@@ -11413,7 +11423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>222</v>
       </c>
@@ -11499,7 +11509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>224</v>
       </c>
@@ -11585,7 +11595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>226</v>
       </c>
@@ -11671,7 +11681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>228</v>
       </c>
@@ -11757,7 +11767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>230</v>
       </c>
@@ -11843,7 +11853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>232</v>
       </c>
@@ -11929,7 +11939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>234</v>
       </c>
@@ -12015,7 +12025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>236</v>
       </c>
@@ -12101,7 +12111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>238</v>
       </c>
@@ -12187,7 +12197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>240</v>
       </c>
@@ -12273,7 +12283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>242</v>
       </c>
@@ -12359,7 +12369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>244</v>
       </c>
@@ -12445,7 +12455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>246</v>
       </c>
@@ -12531,7 +12541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>248</v>
       </c>
@@ -12617,7 +12627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>250</v>
       </c>
@@ -12703,7 +12713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>252</v>
       </c>
@@ -12789,7 +12799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>254</v>
       </c>
@@ -12875,7 +12885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>256</v>
       </c>
@@ -12961,7 +12971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>258</v>
       </c>
@@ -13047,7 +13057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>260</v>
       </c>
@@ -13133,7 +13143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>262</v>
       </c>
@@ -13219,7 +13229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>264</v>
       </c>
@@ -13305,7 +13315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>266</v>
       </c>
@@ -13391,7 +13401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>268</v>
       </c>
@@ -13477,7 +13487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>270</v>
       </c>
@@ -13563,7 +13573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>272</v>
       </c>
@@ -13649,7 +13659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>274</v>
       </c>
@@ -13735,7 +13745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>276</v>
       </c>
@@ -13821,7 +13831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>278</v>
       </c>
@@ -13907,7 +13917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>280</v>
       </c>
@@ -13993,7 +14003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>282</v>
       </c>
@@ -14079,7 +14089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>284</v>
       </c>
@@ -14165,7 +14175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>286</v>
       </c>
@@ -14251,7 +14261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>288</v>
       </c>
@@ -14337,7 +14347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>290</v>
       </c>
@@ -14423,7 +14433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>292</v>
       </c>
@@ -14509,7 +14519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>294</v>
       </c>
@@ -14595,7 +14605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>296</v>
       </c>
@@ -14681,7 +14691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>298</v>
       </c>
@@ -14767,7 +14777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>300</v>
       </c>
@@ -14853,7 +14863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>302</v>
       </c>
@@ -14939,7 +14949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>304</v>
       </c>
@@ -15025,7 +15035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>306</v>
       </c>
@@ -15111,7 +15121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>308</v>
       </c>
@@ -15197,7 +15207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>310</v>
       </c>
@@ -15283,7 +15293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>312</v>
       </c>
@@ -15369,7 +15379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>314</v>
       </c>
@@ -15455,7 +15465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>316</v>
       </c>
@@ -15541,7 +15551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>318</v>
       </c>
@@ -15627,7 +15637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>320</v>
       </c>
@@ -15713,7 +15723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>322</v>
       </c>
@@ -15799,7 +15809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>324</v>
       </c>
@@ -15885,7 +15895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>326</v>
       </c>
@@ -15971,7 +15981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>328</v>
       </c>
@@ -16057,7 +16067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>330</v>
       </c>
@@ -16143,7 +16153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>332</v>
       </c>
@@ -16229,7 +16239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>334</v>
       </c>
@@ -16315,7 +16325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>336</v>
       </c>
@@ -16401,7 +16411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>338</v>
       </c>
@@ -16487,7 +16497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>340</v>
       </c>
@@ -16573,7 +16583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>342</v>
       </c>
@@ -16659,7 +16669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>344</v>
       </c>
@@ -16745,7 +16755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>346</v>
       </c>
@@ -16831,7 +16841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>348</v>
       </c>
@@ -16917,7 +16927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>350</v>
       </c>
@@ -17003,7 +17013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>352</v>
       </c>
@@ -17089,7 +17099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>354</v>
       </c>
@@ -17175,7 +17185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>356</v>
       </c>
@@ -17261,7 +17271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>358</v>
       </c>
@@ -17347,7 +17357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>360</v>
       </c>
@@ -17433,7 +17443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>362</v>
       </c>
@@ -17519,7 +17529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>364</v>
       </c>
@@ -17605,7 +17615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>366</v>
       </c>
@@ -17691,7 +17701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>368</v>
       </c>
@@ -17777,7 +17787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>370</v>
       </c>
@@ -17863,7 +17873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>372</v>
       </c>
@@ -17949,7 +17959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>374</v>
       </c>
@@ -18035,7 +18045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>376</v>
       </c>
@@ -18121,7 +18131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>378</v>
       </c>
@@ -18207,7 +18217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>380</v>
       </c>
@@ -18293,7 +18303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>382</v>
       </c>
@@ -18379,7 +18389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>384</v>
       </c>
@@ -18465,7 +18475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>386</v>
       </c>
@@ -18551,7 +18561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>388</v>
       </c>
@@ -18637,7 +18647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>390</v>
       </c>
@@ -18723,7 +18733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>392</v>
       </c>
@@ -18809,7 +18819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>394</v>
       </c>
@@ -18895,7 +18905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>396</v>
       </c>
@@ -18981,7 +18991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>398</v>
       </c>
@@ -19067,7 +19077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>400</v>
       </c>
@@ -19153,7 +19163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>402</v>
       </c>
@@ -19239,7 +19249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>404</v>
       </c>
@@ -19325,7 +19335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>406</v>
       </c>
@@ -19411,7 +19421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>408</v>
       </c>
@@ -19497,7 +19507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>410</v>
       </c>
@@ -19583,7 +19593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>412</v>
       </c>
@@ -19669,7 +19679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>414</v>
       </c>
@@ -19755,7 +19765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>416</v>
       </c>
@@ -19841,7 +19851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>418</v>
       </c>
@@ -19927,7 +19937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>420</v>
       </c>
@@ -20013,7 +20023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>422</v>
       </c>
@@ -20099,7 +20109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>424</v>
       </c>
@@ -20185,7 +20195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>426</v>
       </c>
@@ -20271,7 +20281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>428</v>
       </c>
@@ -20357,7 +20367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>430</v>
       </c>
@@ -20443,7 +20453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>432</v>
       </c>
@@ -20529,7 +20539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>434</v>
       </c>
@@ -20615,7 +20625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>436</v>
       </c>
@@ -20701,7 +20711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>438</v>
       </c>
@@ -20787,7 +20797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>440</v>
       </c>
@@ -20873,7 +20883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>442</v>
       </c>
@@ -20959,7 +20969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>444</v>
       </c>
@@ -21045,7 +21055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>446</v>
       </c>
@@ -21131,7 +21141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>448</v>
       </c>
@@ -21217,7 +21227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>450</v>
       </c>
@@ -21303,7 +21313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>452</v>
       </c>
@@ -21389,7 +21399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>454</v>
       </c>
@@ -21475,7 +21485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>456</v>
       </c>
@@ -21561,7 +21571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>458</v>
       </c>
@@ -21647,7 +21657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>460</v>
       </c>
@@ -21733,7 +21743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>462</v>
       </c>
@@ -21819,7 +21829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>464</v>
       </c>
@@ -21905,7 +21915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>466</v>
       </c>
@@ -21991,7 +22001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>468</v>
       </c>
@@ -22077,7 +22087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>470</v>
       </c>
@@ -22163,7 +22173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>472</v>
       </c>
@@ -22249,7 +22259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>474</v>
       </c>
@@ -22335,7 +22345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>476</v>
       </c>
@@ -22421,7 +22431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>478</v>
       </c>
@@ -22507,7 +22517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>480</v>
       </c>
@@ -22593,7 +22603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>482</v>
       </c>
@@ -22679,7 +22689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>484</v>
       </c>
@@ -22765,7 +22775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>486</v>
       </c>
@@ -22851,7 +22861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>488</v>
       </c>
@@ -22937,7 +22947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>490</v>
       </c>
@@ -23023,7 +23033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>492</v>
       </c>
@@ -23109,7 +23119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>494</v>
       </c>
@@ -23195,7 +23205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>496</v>
       </c>
@@ -23281,7 +23291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>498</v>
       </c>
@@ -23367,7 +23377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>500</v>
       </c>
@@ -23453,7 +23463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>502</v>
       </c>
@@ -23539,7 +23549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>504</v>
       </c>
@@ -23625,7 +23635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>506</v>
       </c>
@@ -23711,7 +23721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>508</v>
       </c>
@@ -23797,7 +23807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>510</v>
       </c>
@@ -23883,7 +23893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>512</v>
       </c>
@@ -23969,7 +23979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>514</v>
       </c>
@@ -24055,7 +24065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>516</v>
       </c>
@@ -24141,7 +24151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>518</v>
       </c>
@@ -24227,7 +24237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>520</v>
       </c>
@@ -24313,7 +24323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>522</v>
       </c>
@@ -24399,7 +24409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>524</v>
       </c>
@@ -24485,7 +24495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>526</v>
       </c>
@@ -24571,7 +24581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>528</v>
       </c>
@@ -24657,7 +24667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>530</v>
       </c>
@@ -24743,7 +24753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>532</v>
       </c>
@@ -24829,7 +24839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>534</v>
       </c>
@@ -24915,7 +24925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>536</v>
       </c>
@@ -25001,7 +25011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>538</v>
       </c>
@@ -25087,7 +25097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>540</v>
       </c>
@@ -25173,7 +25183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>542</v>
       </c>
@@ -25259,7 +25269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>544</v>
       </c>
@@ -25345,7 +25355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>546</v>
       </c>
@@ -25431,7 +25441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>548</v>
       </c>
@@ -25517,7 +25527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>550</v>
       </c>
@@ -25603,7 +25613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>552</v>
       </c>
@@ -25689,7 +25699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>554</v>
       </c>
@@ -25775,7 +25785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>556</v>
       </c>
@@ -25861,7 +25871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>558</v>
       </c>
@@ -25947,7 +25957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>560</v>
       </c>
@@ -26033,7 +26043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>562</v>
       </c>
@@ -26119,7 +26129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>564</v>
       </c>
@@ -26205,7 +26215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>566</v>
       </c>
@@ -26291,7 +26301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>568</v>
       </c>
@@ -26377,7 +26387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>570</v>
       </c>
@@ -26463,7 +26473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>572</v>
       </c>
@@ -26549,7 +26559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>574</v>
       </c>
@@ -26635,7 +26645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>576</v>
       </c>
@@ -26721,7 +26731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>578</v>
       </c>
@@ -26807,7 +26817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>580</v>
       </c>
@@ -26893,7 +26903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>582</v>
       </c>
@@ -26979,7 +26989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>584</v>
       </c>
@@ -27065,7 +27075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>586</v>
       </c>
@@ -27151,7 +27161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>588</v>
       </c>
@@ -27237,7 +27247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>590</v>
       </c>
@@ -27323,7 +27333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>592</v>
       </c>
@@ -27409,7 +27419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>594</v>
       </c>
@@ -27495,7 +27505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>595</v>
       </c>
@@ -27581,7 +27591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>597</v>
       </c>
@@ -27667,7 +27677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>599</v>
       </c>
@@ -27753,7 +27763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>601</v>
       </c>
@@ -27836,7 +27846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>602</v>
       </c>
@@ -27919,7 +27929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>603</v>
       </c>
@@ -28005,7 +28015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>605</v>
       </c>
@@ -28091,7 +28101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>607</v>
       </c>
@@ -28177,7 +28187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>609</v>
       </c>
@@ -28263,7 +28273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>611</v>
       </c>
@@ -28349,7 +28359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>613</v>
       </c>
@@ -28435,7 +28445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>615</v>
       </c>
@@ -28521,7 +28531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>617</v>
       </c>
@@ -28607,7 +28617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>619</v>
       </c>
@@ -28693,7 +28703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>621</v>
       </c>
@@ -28779,7 +28789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>623</v>
       </c>
@@ -28865,7 +28875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>625</v>
       </c>
@@ -28951,7 +28961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>627</v>
       </c>
@@ -29037,7 +29047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>629</v>
       </c>
@@ -29123,7 +29133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
         <v>631</v>
       </c>
@@ -29209,7 +29219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>633</v>
       </c>
@@ -29295,7 +29305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>635</v>
       </c>
@@ -29381,7 +29391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>637</v>
       </c>
@@ -29467,7 +29477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
         <v>639</v>
       </c>
@@ -29553,7 +29563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>641</v>
       </c>
@@ -29639,7 +29649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
         <v>643</v>
       </c>
@@ -29725,7 +29735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
         <v>645</v>
       </c>
@@ -29811,7 +29821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
         <v>647</v>
       </c>
@@ -29897,7 +29907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
         <v>649</v>
       </c>
@@ -29983,7 +29993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
         <v>651</v>
       </c>
@@ -30069,7 +30079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>653</v>
       </c>
@@ -30155,7 +30165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>655</v>
       </c>
@@ -30241,7 +30251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
         <v>657</v>
       </c>
@@ -30327,7 +30337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
         <v>659</v>
       </c>
@@ -30413,7 +30423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
         <v>661</v>
       </c>
@@ -30499,7 +30509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
         <v>663</v>
       </c>
@@ -30585,7 +30595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
         <v>665</v>
       </c>
@@ -30671,7 +30681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
         <v>667</v>
       </c>
@@ -30757,7 +30767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>669</v>
       </c>
@@ -30843,7 +30853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>671</v>
       </c>
@@ -30929,7 +30939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>673</v>
       </c>
@@ -31015,7 +31025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>675</v>
       </c>
@@ -31101,7 +31111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>677</v>
       </c>
@@ -31187,7 +31197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>679</v>
       </c>
@@ -31273,7 +31283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>681</v>
       </c>
@@ -31359,7 +31369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>683</v>
       </c>
@@ -31445,7 +31455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>685</v>
       </c>
@@ -31531,7 +31541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>687</v>
       </c>
@@ -31617,7 +31627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
         <v>689</v>
       </c>
@@ -31703,7 +31713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
         <v>691</v>
       </c>
@@ -31789,7 +31799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>693</v>
       </c>
@@ -31875,7 +31885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>695</v>
       </c>
@@ -31961,7 +31971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>697</v>
       </c>
@@ -32047,7 +32057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>699</v>
       </c>
@@ -32133,7 +32143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>701</v>
       </c>
@@ -32219,7 +32229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>703</v>
       </c>
@@ -32305,7 +32315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>705</v>
       </c>
@@ -32391,7 +32401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>707</v>
       </c>
@@ -32477,7 +32487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>709</v>
       </c>
@@ -32563,7 +32573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>711</v>
       </c>
@@ -32649,7 +32659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
         <v>713</v>
       </c>
@@ -32735,7 +32745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
         <v>715</v>
       </c>
@@ -32821,7 +32831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
         <v>717</v>
       </c>
@@ -32907,7 +32917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
         <v>719</v>
       </c>
@@ -32993,7 +33003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>721</v>
       </c>
@@ -33079,7 +33089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>723</v>
       </c>
@@ -33165,7 +33175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>725</v>
       </c>
@@ -33251,7 +33261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
         <v>727</v>
       </c>
@@ -33337,7 +33347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
         <v>729</v>
       </c>
@@ -33423,7 +33433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>731</v>
       </c>
@@ -33509,7 +33519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
         <v>733</v>
       </c>
@@ -33595,7 +33605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>735</v>
       </c>
@@ -33681,7 +33691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
         <v>737</v>
       </c>
@@ -33767,7 +33777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
         <v>739</v>
       </c>
@@ -33853,7 +33863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
         <v>741</v>
       </c>
@@ -33939,7 +33949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>743</v>
       </c>
@@ -34025,7 +34035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
         <v>745</v>
       </c>
@@ -34111,7 +34121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
         <v>747</v>
       </c>
@@ -34197,7 +34207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
         <v>749</v>
       </c>
@@ -34283,7 +34293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>751</v>
       </c>
@@ -34369,7 +34379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>753</v>
       </c>
@@ -34455,7 +34465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
         <v>755</v>
       </c>
@@ -34541,7 +34551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
         <v>757</v>
       </c>
@@ -34627,7 +34637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
         <v>759</v>
       </c>
@@ -34713,7 +34723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
         <v>761</v>
       </c>
@@ -34799,7 +34809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
         <v>763</v>
       </c>
@@ -34885,7 +34895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
         <v>765</v>
       </c>
@@ -34971,7 +34981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
         <v>767</v>
       </c>
@@ -35057,7 +35067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
         <v>769</v>
       </c>
@@ -35143,7 +35153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
         <v>771</v>
       </c>
@@ -35229,7 +35239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
         <v>773</v>
       </c>
@@ -35315,7 +35325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
         <v>775</v>
       </c>
@@ -35401,7 +35411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
         <v>776</v>
       </c>
@@ -35487,7 +35497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
         <v>778</v>
       </c>
@@ -35573,7 +35583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
         <v>780</v>
       </c>
@@ -35659,7 +35669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
         <v>782</v>
       </c>
@@ -35745,7 +35755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
         <v>784</v>
       </c>
@@ -35831,7 +35841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
         <v>786</v>
       </c>
@@ -35917,7 +35927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
         <v>788</v>
       </c>
@@ -36003,7 +36013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
         <v>790</v>
       </c>
@@ -36089,7 +36099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
         <v>792</v>
       </c>
@@ -36175,7 +36185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
         <v>794</v>
       </c>
@@ -36261,7 +36271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
         <v>796</v>
       </c>
@@ -36347,7 +36357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
         <v>798</v>
       </c>
@@ -36433,7 +36443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
         <v>800</v>
       </c>
@@ -36519,7 +36529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
         <v>802</v>
       </c>
@@ -36605,7 +36615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>804</v>
       </c>
@@ -36691,7 +36701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>806</v>
       </c>
@@ -36777,7 +36787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
         <v>808</v>
       </c>
@@ -36863,7 +36873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
         <v>810</v>
       </c>
@@ -36949,7 +36959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
         <v>812</v>
       </c>
@@ -37035,7 +37045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
         <v>814</v>
       </c>
@@ -37121,7 +37131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
         <v>816</v>
       </c>
@@ -37207,7 +37217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
         <v>818</v>
       </c>
@@ -37293,7 +37303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
         <v>820</v>
       </c>
@@ -37379,7 +37389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
         <v>822</v>
       </c>
@@ -37465,7 +37475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
         <v>824</v>
       </c>
@@ -37551,7 +37561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
         <v>826</v>
       </c>
@@ -37637,7 +37647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
         <v>828</v>
       </c>
@@ -37723,7 +37733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>830</v>
       </c>
@@ -37809,7 +37819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
         <v>832</v>
       </c>
@@ -37895,7 +37905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>834</v>
       </c>
@@ -37981,7 +37991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>836</v>
       </c>
@@ -38067,7 +38077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
         <v>838</v>
       </c>
@@ -38153,7 +38163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
         <v>840</v>
       </c>
@@ -38239,7 +38249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
         <v>842</v>
       </c>
@@ -38325,7 +38335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
         <v>844</v>
       </c>
@@ -38411,7 +38421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
         <v>846</v>
       </c>
@@ -38497,7 +38507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
         <v>848</v>
       </c>
@@ -38583,7 +38593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
         <v>850</v>
       </c>
@@ -38669,7 +38679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
         <v>852</v>
       </c>
@@ -38755,7 +38765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
         <v>854</v>
       </c>
@@ -38841,7 +38851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
         <v>856</v>
       </c>
@@ -38927,7 +38937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
         <v>858</v>
       </c>
@@ -39013,7 +39023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
         <v>860</v>
       </c>
@@ -39099,7 +39109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
         <v>862</v>
       </c>
@@ -39185,7 +39195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
         <v>864</v>
       </c>
@@ -39271,7 +39281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
         <v>866</v>
       </c>
@@ -39357,7 +39367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
         <v>868</v>
       </c>
@@ -39443,7 +39453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
         <v>870</v>
       </c>
@@ -39529,7 +39539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
         <v>872</v>
       </c>
@@ -39615,7 +39625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
         <v>874</v>
       </c>
@@ -39701,7 +39711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
         <v>876</v>
       </c>
@@ -39787,7 +39797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
         <v>878</v>
       </c>
@@ -39873,7 +39883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
         <v>880</v>
       </c>
@@ -39959,7 +39969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
         <v>882</v>
       </c>
@@ -40045,7 +40055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
         <v>884</v>
       </c>
@@ -40131,7 +40141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
         <v>886</v>
       </c>
@@ -40217,7 +40227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
         <v>888</v>
       </c>
@@ -40303,7 +40313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
         <v>890</v>
       </c>
@@ -40389,7 +40399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
         <v>892</v>
       </c>
@@ -40475,7 +40485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
         <v>894</v>
       </c>
@@ -40561,7 +40571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
         <v>896</v>
       </c>
@@ -40647,7 +40657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
         <v>898</v>
       </c>
@@ -40733,7 +40743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
         <v>900</v>
       </c>
@@ -40819,7 +40829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
         <v>902</v>
       </c>
@@ -40905,7 +40915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
         <v>904</v>
       </c>
@@ -40991,7 +41001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
         <v>906</v>
       </c>
@@ -41077,7 +41087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
         <v>908</v>
       </c>
@@ -41163,7 +41173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
         <v>910</v>
       </c>
@@ -41249,7 +41259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
         <v>912</v>
       </c>
@@ -41335,7 +41345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
         <v>914</v>
       </c>
@@ -41421,7 +41431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
         <v>916</v>
       </c>
@@ -41507,7 +41517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
         <v>918</v>
       </c>
@@ -41593,7 +41603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
         <v>920</v>
       </c>
@@ -41679,7 +41689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
         <v>922</v>
       </c>
@@ -41765,7 +41775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
         <v>924</v>
       </c>
@@ -41851,7 +41861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
         <v>926</v>
       </c>
@@ -41937,7 +41947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
         <v>928</v>
       </c>
@@ -42023,7 +42033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
         <v>930</v>
       </c>
@@ -42109,7 +42119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
         <v>932</v>
       </c>
@@ -42195,7 +42205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
         <v>934</v>
       </c>
@@ -42281,7 +42291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:28" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:28" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="12" t="s">
         <v>936</v>
       </c>
@@ -42364,7 +42374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:28" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:28" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="12" t="s">
         <v>937</v>
       </c>
@@ -42447,7 +42457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
         <v>938</v>
       </c>
@@ -42533,7 +42543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
         <v>940</v>
       </c>
@@ -42619,7 +42629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
         <v>942</v>
       </c>
@@ -42705,7 +42715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
         <v>944</v>
       </c>
@@ -42791,7 +42801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
         <v>946</v>
       </c>
@@ -42877,7 +42887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="s">
         <v>948</v>
       </c>
@@ -42963,7 +42973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
         <v>950</v>
       </c>
@@ -43049,7 +43059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
         <v>952</v>
       </c>
@@ -43135,7 +43145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
         <v>954</v>
       </c>
@@ -43221,7 +43231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
         <v>956</v>
       </c>
@@ -43307,7 +43317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
         <v>958</v>
       </c>
@@ -43393,7 +43403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A464" s="2" t="s">
         <v>960</v>
       </c>
@@ -43479,7 +43489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
         <v>962</v>
       </c>
@@ -43565,7 +43575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
         <v>964</v>
       </c>
@@ -43651,7 +43661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
         <v>966</v>
       </c>
@@ -43737,7 +43747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
         <v>968</v>
       </c>
@@ -43823,7 +43833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
         <v>970</v>
       </c>
@@ -43917,7 +43927,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -43931,7 +43941,7 @@
     <col min="10" max="22" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>972</v>
       </c>
@@ -43957,7 +43967,7 @@
       <c r="U1" s="15"/>
       <c r="V1" s="15"/>
     </row>
-    <row r="2" spans="1:22" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>973</v>
       </c>
@@ -43983,7 +43993,7 @@
       <c r="U2" s="15"/>
       <c r="V2" s="15"/>
     </row>
-    <row r="3" spans="1:22" ht="123.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="123.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -44051,7 +44061,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -44095,7 +44105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>975</v>
       </c>
@@ -44163,7 +44173,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>982</v>
       </c>
@@ -44231,7 +44241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>985</v>
       </c>
@@ -44293,7 +44303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>985</v>
       </c>
@@ -44355,7 +44365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>982</v>
       </c>
@@ -44423,7 +44433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>985</v>
       </c>
@@ -44485,7 +44495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>985</v>
       </c>
@@ -44547,7 +44557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>982</v>
       </c>
@@ -44615,7 +44625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>985</v>
       </c>
@@ -44677,7 +44687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>985</v>
       </c>
@@ -44739,7 +44749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>982</v>
       </c>
@@ -44807,7 +44817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>985</v>
       </c>
@@ -44869,7 +44879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>985</v>
       </c>
@@ -44931,7 +44941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>982</v>
       </c>
@@ -44999,7 +45009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>985</v>
       </c>
@@ -45061,7 +45071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>985</v>
       </c>
@@ -45123,7 +45133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>982</v>
       </c>
@@ -45191,7 +45201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>985</v>
       </c>
@@ -45253,7 +45263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>985</v>
       </c>
@@ -45315,7 +45325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>982</v>
       </c>
@@ -45383,7 +45393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>985</v>
       </c>
@@ -45445,7 +45455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>985</v>
       </c>
@@ -45507,7 +45517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>982</v>
       </c>
@@ -45575,7 +45585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>985</v>
       </c>
@@ -45637,7 +45647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>985</v>
       </c>
